--- a/tools/importer/reports/import.report.xlsx
+++ b/tools/importer/reports/import.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="114">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,28 +40,64 @@
     <t>url</t>
   </si>
   <si>
+    <t>community.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns-featured","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","accordion-faq"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:07:37.921Z</t>
+  </si>
+  <si>
+    <t>Community — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/community.html</t>
+  </si>
+  <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-gallery","ticker","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:07:32.561Z</t>
+  </si>
+  <si>
+    <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/index.html</t>
+  </si>
+  <si>
     <t>wknd/about.report.json</t>
   </si>
   <si>
     <t>["hero","tabs-team","columns-about","cards-feature","cards-article"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>wknd/about</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>2026-03-26T17:44:33.555Z</t>
   </si>
   <si>
     <t>About — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/about.html</t>
+    <t>https://wknd-adventures.com/about.html</t>
   </si>
   <si>
     <t>wknd/adventures.report.json</t>
@@ -79,25 +115,16 @@
     <t>Adventures — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/adventures.html</t>
+    <t>https://wknd-adventures.com/adventures.html</t>
   </si>
   <si>
     <t>wknd/community.report.json</t>
   </si>
   <si>
-    <t>["hero","columns-featured","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","accordion-faq"]</t>
-  </si>
-  <si>
     <t>wknd/community</t>
   </si>
   <si>
     <t>2026-03-26T17:44:24.977Z</t>
-  </si>
-  <si>
-    <t>Community — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://gabrielwalt.github.io/wknd/community.html</t>
   </si>
   <si>
     <t>wknd/destinations.html.report.json</t>
@@ -120,7 +147,7 @@
     <t>2026-03-25T23:39:23.930Z</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/destinations.html</t>
+    <t>https://wknd-adventures.com/destinations.html</t>
   </si>
   <si>
     <t>wknd/destinations.report.json</t>
@@ -153,7 +180,7 @@
     <t>Expeditions — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/expeditions.html</t>
+    <t>https://wknd-adventures.com/expeditions.html</t>
   </si>
   <si>
     <t>wknd/faq.report.json</t>
@@ -171,7 +198,7 @@
     <t>Questions — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/faq.html</t>
+    <t>https://wknd-adventures.com/faq.html</t>
   </si>
   <si>
     <t>wknd/field-notes.report.json</t>
@@ -189,7 +216,7 @@
     <t>Field Notes — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/field-notes</t>
+    <t>https://wknd-adventures.com/field-notes</t>
   </si>
   <si>
     <t>wknd/gear.report.json</t>
@@ -207,27 +234,18 @@
     <t>Gear — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/gear.html</t>
+    <t>https://wknd-adventures.com/gear.html</t>
   </si>
   <si>
     <t>wknd/index.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-gallery","ticker","accordion-faq"]</t>
-  </si>
-  <si>
     <t>wknd/index</t>
   </si>
   <si>
     <t>2026-03-26T17:44:09.352Z</t>
   </si>
   <si>
-    <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
-  </si>
-  <si>
-    <t>https://gabrielwalt.github.io/wknd/index.html</t>
-  </si>
-  <si>
     <t>wknd/sustainability.report.json</t>
   </si>
   <si>
@@ -243,7 +261,7 @@
     <t>Wild Ethics — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/sustainability.html</t>
+    <t>https://wknd-adventures.com/sustainability.html</t>
   </si>
   <si>
     <t>wknd/blog/alpine-cycling.report.json</t>
@@ -261,7 +279,7 @@
     <t>Six Days Through the High Alps — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/alpine-cycling.html</t>
+    <t>https://wknd-adventures.com/blog/alpine-cycling.html</t>
   </si>
   <si>
     <t>wknd/blog/kayaking-norway.report.json</t>
@@ -276,7 +294,7 @@
     <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/kayaking-norway.html</t>
+    <t>https://wknd-adventures.com/blog/kayaking-norway.html</t>
   </si>
   <si>
     <t>wknd/blog/mountain-photography.report.json</t>
@@ -291,7 +309,7 @@
     <t>The Camera on Your Back — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/mountain-photography.html</t>
+    <t>https://wknd-adventures.com/blog/mountain-photography.html</t>
   </si>
   <si>
     <t>wknd/blog/patagonia-trek.report.json</t>
@@ -306,7 +324,7 @@
     <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/patagonia-trek.html</t>
+    <t>https://wknd-adventures.com/blog/patagonia-trek.html</t>
   </si>
   <si>
     <t>wknd/blog/ultralight-backpacking.report.json</t>
@@ -321,7 +339,7 @@
     <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/ultralight-backpacking.html</t>
+    <t>https://wknd-adventures.com/blog/ultralight-backpacking.html</t>
   </si>
   <si>
     <t>wknd/blog/yosemite-rock-climbing.report.json</t>
@@ -336,7 +354,7 @@
     <t>First Light on the Valley — WKND Adventures</t>
   </si>
   <si>
-    <t>https://gabrielwalt.github.io/wknd/blog/yosemite-rock-climbing.html</t>
+    <t>https://wknd-adventures.com/blog/yosemite-rock-climbing.html</t>
   </si>
 </sst>
 </file>
@@ -725,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -856,239 +874,239 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>49</v>
       </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="H9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="I9" t="s">
         <v>55</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
+      <c r="H10" t="s">
         <v>60</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="I10" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
+      <c r="H11" t="s">
         <v>66</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="I11" t="s">
         <v>67</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" t="s">
+      <c r="H12" t="s">
         <v>72</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="I12" t="s">
         <v>73</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -1097,24 +1115,24 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
@@ -1126,135 +1144,193 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" t="s">
         <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" t="s">
         <v>93</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
         <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" t="s">
         <v>103</v>
       </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>104</v>
       </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
         <v>105</v>
       </c>
-      <c r="H18" t="s">
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
         <v>106</v>
       </c>
-      <c r="I18" t="s">
+      <c r="H19" t="s">
         <v>107</v>
+      </c>
+      <c r="I19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import.report.xlsx
+++ b/tools/importer/reports/import.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="156">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,22 +40,58 @@
     <t>url</t>
   </si>
   <si>
+    <t>about.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-team","columns-about","cards-feature","cards-article"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:18.721Z</t>
+  </si>
+  <si>
+    <t>About — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/about.html</t>
+  </si>
+  <si>
+    <t>adventures.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-promo","cards-article"]</t>
+  </si>
+  <si>
+    <t>adventures</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:03.398Z</t>
+  </si>
+  <si>
+    <t>Adventures — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/adventures.html</t>
+  </si>
+  <si>
     <t>community.report.json</t>
   </si>
   <si>
     <t>["hero","columns-featured","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","accordion-faq"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>community</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-04-12T15:07:37.921Z</t>
+    <t>2026-04-12T15:08:11.049Z</t>
   </si>
   <si>
     <t>Community — WKND Adventures</t>
@@ -64,6 +100,96 @@
     <t>https://wknd-adventures.com/community.html</t>
   </si>
   <si>
+    <t>destinations.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
+  </si>
+  <si>
+    <t>destinations</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:28.934Z</t>
+  </si>
+  <si>
+    <t>Destinations — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/destinations.html</t>
+  </si>
+  <si>
+    <t>expeditions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","columns-numbered","columns-numbered","columns-promo","cards-article"]</t>
+  </si>
+  <si>
+    <t>expeditions</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:34.232Z</t>
+  </si>
+  <si>
+    <t>Expeditions — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/expeditions.html</t>
+  </si>
+  <si>
+    <t>faq.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns-promo","cards-article","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:24.726Z</t>
+  </si>
+  <si>
+    <t>Questions — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/faq.html</t>
+  </si>
+  <si>
+    <t>field-notes.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","columns-featured","columns-promo"]</t>
+  </si>
+  <si>
+    <t>field-notes</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:07.239Z</t>
+  </si>
+  <si>
+    <t>Field Notes — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/field-notes</t>
+  </si>
+  <si>
+    <t>gear.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","tabs","columns-featured","columns-numbered","cards-feature"]</t>
+  </si>
+  <si>
+    <t>gear</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:39.596Z</t>
+  </si>
+  <si>
+    <t>Gear — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/gear.html</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -73,7 +199,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-04-12T15:07:32.561Z</t>
+    <t>2026-04-12T15:08:00.266Z</t>
   </si>
   <si>
     <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
@@ -82,40 +208,133 @@
     <t>https://wknd-adventures.com/index.html</t>
   </si>
   <si>
+    <t>sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs","columns-featured","columns-numbered","columns-about","cards-feature","cards-article"]</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:14.754Z</t>
+  </si>
+  <si>
+    <t>Wild Ethics — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/sustainability.html</t>
+  </si>
+  <si>
+    <t>blog/alpine-cycling.report.json</t>
+  </si>
+  <si>
+    <t>["hero-article","columns-sidebar","cards-article","columns-gallery"]</t>
+  </si>
+  <si>
+    <t>blog/alpine-cycling</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:52.540Z</t>
+  </si>
+  <si>
+    <t>Six Days Through the High Alps — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/alpine-cycling.html</t>
+  </si>
+  <si>
+    <t>blog/kayaking-norway.report.json</t>
+  </si>
+  <si>
+    <t>blog/kayaking-norway</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:48.671Z</t>
+  </si>
+  <si>
+    <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/kayaking-norway.html</t>
+  </si>
+  <si>
+    <t>blog/mountain-photography.report.json</t>
+  </si>
+  <si>
+    <t>blog/mountain-photography</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:09:02.008Z</t>
+  </si>
+  <si>
+    <t>The Camera on Your Back — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/mountain-photography.html</t>
+  </si>
+  <si>
+    <t>blog/patagonia-trek.report.json</t>
+  </si>
+  <si>
+    <t>blog/patagonia-trek</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:43.949Z</t>
+  </si>
+  <si>
+    <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/patagonia-trek.html</t>
+  </si>
+  <si>
+    <t>blog/ultralight-backpacking.report.json</t>
+  </si>
+  <si>
+    <t>blog/ultralight-backpacking</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:09:07.288Z</t>
+  </si>
+  <si>
+    <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/ultralight-backpacking.html</t>
+  </si>
+  <si>
+    <t>blog/yosemite-rock-climbing.report.json</t>
+  </si>
+  <si>
+    <t>blog/yosemite-rock-climbing</t>
+  </si>
+  <si>
+    <t>2026-04-12T15:08:56.062Z</t>
+  </si>
+  <si>
+    <t>First Light on the Valley — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/yosemite-rock-climbing.html</t>
+  </si>
+  <si>
     <t>wknd/about.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-team","columns-about","cards-feature","cards-article"]</t>
-  </si>
-  <si>
     <t>wknd/about</t>
   </si>
   <si>
     <t>2026-03-26T17:44:33.555Z</t>
   </si>
   <si>
-    <t>About — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/about.html</t>
-  </si>
-  <si>
     <t>wknd/adventures.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-promo","cards-article"]</t>
-  </si>
-  <si>
     <t>wknd/adventures</t>
   </si>
   <si>
     <t>2026-03-26T17:44:14.598Z</t>
-  </si>
-  <si>
-    <t>Adventures — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/adventures.html</t>
   </si>
   <si>
     <t>wknd/community.report.json</t>
@@ -147,96 +366,51 @@
     <t>2026-03-25T23:39:23.930Z</t>
   </si>
   <si>
-    <t>https://wknd-adventures.com/destinations.html</t>
-  </si>
-  <si>
     <t>wknd/destinations.report.json</t>
   </si>
   <si>
-    <t>["hero","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
-  </si>
-  <si>
     <t>wknd/destinations</t>
   </si>
   <si>
     <t>2026-03-26T17:44:43.527Z</t>
   </si>
   <si>
-    <t>Destinations — WKND Adventures</t>
-  </si>
-  <si>
     <t>wknd/expeditions.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-activity","columns-numbered","columns-numbered","columns-promo","cards-article"]</t>
-  </si>
-  <si>
     <t>wknd/expeditions</t>
   </si>
   <si>
     <t>2026-03-26T17:44:47.438Z</t>
   </si>
   <si>
-    <t>Expeditions — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/expeditions.html</t>
-  </si>
-  <si>
     <t>wknd/faq.report.json</t>
   </si>
   <si>
-    <t>["hero","columns-promo","cards-article","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq"]</t>
-  </si>
-  <si>
     <t>wknd/faq</t>
   </si>
   <si>
     <t>2026-03-26T17:44:37.734Z</t>
   </si>
   <si>
-    <t>Questions — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/faq.html</t>
-  </si>
-  <si>
     <t>wknd/field-notes.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-activity","columns-featured","columns-promo"]</t>
-  </si>
-  <si>
     <t>wknd/field-notes</t>
   </si>
   <si>
     <t>2026-03-26T17:44:19.880Z</t>
   </si>
   <si>
-    <t>Field Notes — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/field-notes</t>
-  </si>
-  <si>
     <t>wknd/gear.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs-activity","tabs","columns-featured","columns-numbered","cards-feature"]</t>
-  </si>
-  <si>
     <t>wknd/gear</t>
   </si>
   <si>
     <t>2026-03-26T17:44:52.087Z</t>
   </si>
   <si>
-    <t>Gear — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/gear.html</t>
-  </si>
-  <si>
     <t>wknd/index.report.json</t>
   </si>
   <si>
@@ -249,39 +423,21 @@
     <t>wknd/sustainability.report.json</t>
   </si>
   <si>
-    <t>["hero","tabs","columns-featured","columns-numbered","columns-about","cards-feature","cards-article"]</t>
-  </si>
-  <si>
     <t>wknd/sustainability</t>
   </si>
   <si>
     <t>2026-03-26T17:44:28.745Z</t>
   </si>
   <si>
-    <t>Wild Ethics — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/sustainability.html</t>
-  </si>
-  <si>
     <t>wknd/blog/alpine-cycling.report.json</t>
   </si>
   <si>
-    <t>["hero-article","columns-sidebar","cards-article","columns-gallery"]</t>
-  </si>
-  <si>
     <t>wknd/blog/alpine-cycling</t>
   </si>
   <si>
     <t>2026-03-26T17:45:06.425Z</t>
   </si>
   <si>
-    <t>Six Days Through the High Alps — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/alpine-cycling.html</t>
-  </si>
-  <si>
     <t>wknd/blog/kayaking-norway.report.json</t>
   </si>
   <si>
@@ -291,12 +447,6 @@
     <t>2026-03-26T17:45:02.215Z</t>
   </si>
   <si>
-    <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/kayaking-norway.html</t>
-  </si>
-  <si>
     <t>wknd/blog/mountain-photography.report.json</t>
   </si>
   <si>
@@ -306,12 +456,6 @@
     <t>2026-03-26T17:45:17.222Z</t>
   </si>
   <si>
-    <t>The Camera on Your Back — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/mountain-photography.html</t>
-  </si>
-  <si>
     <t>wknd/blog/patagonia-trek.report.json</t>
   </si>
   <si>
@@ -321,12 +465,6 @@
     <t>2026-03-26T17:44:56.785Z</t>
   </si>
   <si>
-    <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/patagonia-trek.html</t>
-  </si>
-  <si>
     <t>wknd/blog/ultralight-backpacking.report.json</t>
   </si>
   <si>
@@ -336,12 +474,6 @@
     <t>2026-03-26T17:45:22.004Z</t>
   </si>
   <si>
-    <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/ultralight-backpacking.html</t>
-  </si>
-  <si>
     <t>wknd/blog/yosemite-rock-climbing.report.json</t>
   </si>
   <si>
@@ -349,12 +481,6 @@
   </si>
   <si>
     <t>2026-03-26T17:45:10.976Z</t>
-  </si>
-  <si>
-    <t>First Light on the Valley — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/yosemite-rock-climbing.html</t>
   </si>
 </sst>
 </file>
@@ -743,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -903,7 +1029,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -912,56 +1038,56 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -970,27 +1096,27 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -999,27 +1125,27 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -1028,27 +1154,27 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1057,27 +1183,27 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -1086,27 +1212,27 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -1115,27 +1241,27 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -1144,27 +1270,27 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -1173,27 +1299,27 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1202,27 +1328,27 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -1231,27 +1357,27 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1260,27 +1386,27 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1289,48 +1415,454 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
         <v>109</v>
       </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
         <v>110</v>
       </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>111</v>
       </c>
-      <c r="H20" t="s">
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
         <v>112</v>
       </c>
-      <c r="I20" t="s">
+      <c r="D21" t="s">
         <v>113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
